--- a/current.xlsx
+++ b/current.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F539"/>
+  <dimension ref="A1:F538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>涞寅路邮政所</t>
+          <t>小昆山邮政支局</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16008</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16009</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>小昆山邮政支局</t>
+          <t>大港邮政所</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16009</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16010</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>大港邮政所</t>
+          <t>东开邮政支局</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16010</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16011</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>东开邮政支局</t>
+          <t>五龙邮政所</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16011</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16012</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>五龙邮政所</t>
+          <t>中山邮政所</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16012</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16013</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>中山邮政所</t>
+          <t>龙源路邮政支局</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16013</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16014</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>龙源路邮政支局</t>
+          <t>南期昌路邮政所</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16014</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16015</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>南期昌路邮政所</t>
+          <t>文汇路邮政所</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16015</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16016</t>
         </is>
       </c>
     </row>
@@ -6568,17 +6568,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>徐汇区</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>徐汇区</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>文汇路邮政所</t>
+          <t>徐汇邮政支局</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16016</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16017</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>徐汇邮政支局</t>
+          <t>衡山路邮政所</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16017</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16018</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>衡山路邮政所</t>
+          <t>武康大楼邮政所</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16018</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16019</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>武康大楼邮政所</t>
+          <t>上海体育场邮政支局</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16019</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16020</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>上海体育场邮政支局</t>
+          <t>南丹东路邮政所</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16020</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16021</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>南丹东路邮政所</t>
+          <t>宛平南路邮政所</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16021</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16022</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>宛平南路邮政所</t>
+          <t>乐山路邮政支局</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16022</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16023</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>乐山路邮政支局</t>
+          <t>交通大学邮政所</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16023</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16024</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>交通大学邮政所</t>
+          <t>淮海中路邮政支局</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16024</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16025</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>淮海中路邮政支局</t>
+          <t>陕西南路邮政所</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16025</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16026</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>陕西南路邮政所</t>
+          <t>复兴中路邮政所</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16026</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16027</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>复兴中路邮政所</t>
+          <t>东安路邮政支局</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16027</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16028</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>东安路邮政支局</t>
+          <t>枫林桥邮政所</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16028</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16029</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>枫林桥邮政所</t>
+          <t>大木桥青年邮政所</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16029</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16030</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>大木桥青年邮政所</t>
+          <t>华泾邮政支局</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16030</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16031</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>华泾邮政支局</t>
+          <t>长桥邮政所</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16031</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16032</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>长桥邮政所</t>
+          <t>罗香邮政所</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16032</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16033</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>罗香邮政所</t>
+          <t>园南新村邮政所</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16033</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16034</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>园南新村邮政所</t>
+          <t>港口邮政所</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16034</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16035</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>港口邮政所</t>
+          <t>龙华邮政支局</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16035</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16036</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>龙华邮政支局</t>
+          <t>石龙路邮政所</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16036</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16037</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>石龙路邮政所</t>
+          <t>龙水路邮政所</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16037</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16038</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>龙水路邮政所</t>
+          <t>龙华路邮政所</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16038</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16039</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>龙华路邮政所</t>
+          <t>龙南邮政所</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16039</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16040</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>龙南邮政所</t>
+          <t>漕河泾邮政支局</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16040</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16041</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>漕河泾邮政支局</t>
+          <t>古美新村邮政所</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16041</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16042</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>古美新村邮政所</t>
+          <t>桂林路邮政所</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16042</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16043</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>桂林路邮政所</t>
+          <t>田林新村邮政所</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16043</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16044</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>田林新村邮政所</t>
+          <t>桂林西街邮政所</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16044</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16045</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>桂林西街邮政所</t>
+          <t>习勤路邮政支局</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16045</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16048</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>习勤路邮政支局</t>
+          <t>师范大学邮政所</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16048</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16049</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>师范大学邮政所</t>
+          <t>漕溪新村邮政所</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16049</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16050</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>漕溪新村邮政所</t>
+          <t>康乐邮政所</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16050</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16051</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>康乐邮政所</t>
+          <t>梅陇邮政支局</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16051</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16052</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>梅陇邮政支局</t>
+          <t>百色路邮政所</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16052</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16053</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>百色路邮政所</t>
+          <t>华东理工邮政所</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16053</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16054</t>
         </is>
       </c>
     </row>
@@ -7720,17 +7720,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>徐汇区</t>
+          <t>宝山区</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>徐汇区</t>
+          <t>宝山区</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>华东理工邮政所</t>
+          <t>泗塘邮政支局</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16054</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16055</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>泗塘邮政支局</t>
+          <t>张庙邮政所</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16055</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16056</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>张庙邮政所</t>
+          <t>淞南邮政所</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16056</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16057</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>淞南邮政所</t>
+          <t>大场邮政支局</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16057</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16058</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>大场邮政支局</t>
+          <t>贺兰山路邮政所</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16058</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16059</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>贺兰山路邮政所</t>
+          <t>乾溪邮政所</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16059</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16060</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>乾溪邮政所</t>
+          <t>高境邮政支局</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16060</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16061</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>高境邮政支局</t>
+          <t>长江南路邮政所</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16061</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16062</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>长江南路邮政所</t>
+          <t>三门路邮政所</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16062</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16063</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>三门路邮政所</t>
+          <t>阳曲路邮政所</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16063</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16064</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>阳曲路邮政所</t>
+          <t>大华邮政支局</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16064</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16065</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>大华邮政支局</t>
+          <t>华灵路邮政所</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16065</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16066</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>华灵路邮政所</t>
+          <t>大华二路邮政所</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16066</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16067</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>大华二路邮政所</t>
+          <t>庙行邮政支局</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16067</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16068</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>庙行邮政支局</t>
+          <t>共康邮政所</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16068</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16069</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>共康邮政所</t>
+          <t>聚丰园路邮政支局</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16069</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16070</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>聚丰园路邮政支局</t>
+          <t>锦秋邮政所</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16070</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16071</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>锦秋邮政所</t>
+          <t>友谊路邮政支局</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16071</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16073</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>友谊路邮政支局</t>
+          <t>宝林八村邮政所</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16073</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16074</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>宝林八村邮政所</t>
+          <t>海江路邮政所</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16074</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16075</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>海江路邮政所</t>
+          <t>杨行邮政支局</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16075</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16076</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>杨行邮政支局</t>
+          <t>天馨花园邮政所</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16076</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16077</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>天馨花园邮政所</t>
+          <t>杨泰路邮政所</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16077</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16078</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>杨泰路邮政所</t>
+          <t>顾村邮政支局</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16078</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16079</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>顾村邮政支局</t>
+          <t>新贸路邮政所</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16079</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16080</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>新贸路邮政所</t>
+          <t>共富新村邮政所</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16080</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16081</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>共富新村邮政所</t>
+          <t>刘行邮政支局</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16081</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16082</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>刘行邮政支局</t>
+          <t>菊盛路邮政所</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16082</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16083</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>菊盛路邮政所</t>
+          <t>罗店邮政支局</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16083</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16084</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>罗店邮政支局</t>
+          <t>长浜邮政所</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16084</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16085</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>长浜邮政所</t>
+          <t>罗泾邮政支局</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16085</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16086</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>罗泾邮政支局</t>
+          <t>潘沪路邮政所</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16086</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16087</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>潘沪路邮政所</t>
+          <t>吴淞邮政支局</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16087</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16088</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>吴淞邮政支局</t>
+          <t>海滨新村邮政所</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16088</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16089</t>
         </is>
       </c>
     </row>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>海滨新村邮政所</t>
+          <t>淞青路邮政所</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16089</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16090</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>淞青路邮政所</t>
+          <t>三阳路邮政所</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16090</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16091</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>三阳路邮政所</t>
+          <t>月浦邮政支局</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16091</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16092</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>月浦邮政支局</t>
+          <t>盛桥邮政支局</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16092</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16093</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>盛桥邮政支局</t>
+          <t>绥化路邮政所</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16093</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16094</t>
         </is>
       </c>
     </row>
@@ -8968,17 +8968,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>宝山区</t>
+          <t>虹口区</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>宝山区</t>
+          <t>虹口区</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>绥化路邮政所</t>
+          <t>虹口邮政支局</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16094</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16095</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>虹口邮政支局</t>
+          <t>鲁迅公园邮政支局</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16095</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16097</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>鲁迅公园邮政支局</t>
+          <t>欧阳路邮政所</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16097</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16098</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>欧阳路邮政所</t>
+          <t>华昌路邮政所</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16098</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16099</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>华昌路邮政所</t>
+          <t>北外滩邮政支局</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16099</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16100</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>北外滩邮政支局</t>
+          <t>长治路邮政所</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16100</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16101</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>长治路邮政所</t>
+          <t>唐山路邮政所</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16101</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16102</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>唐山路邮政所</t>
+          <t>广中路邮政支局</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16102</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16103</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>广中路邮政支局</t>
+          <t>广灵二路邮政所</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16103</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16104</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>广灵二路邮政所</t>
+          <t>玉田路邮政所</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16104</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16105</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>玉田路邮政所</t>
+          <t>临平路邮政支局</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16105</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16106</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>临平路邮政支局</t>
+          <t>邮电新村邮政所</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16106</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16108</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>邮电新村邮政所</t>
+          <t>曲阳邮政支局</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16108</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16109</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>曲阳邮政支局</t>
+          <t>运光邮政支局</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16109</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16110</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>运光邮政支局</t>
+          <t>辉河路邮政所</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16110</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16111</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>辉河路邮政所</t>
+          <t>大连西路邮政所</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16111</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16112</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>大连西路邮政所</t>
+          <t>车站北路邮政支局</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16112</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16113</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>车站北路邮政支局</t>
+          <t>江湾邮政支局</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16113</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16114</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>江湾邮政支局</t>
+          <t>丰镇邮政所</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16114</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16115</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>丰镇邮政所</t>
+          <t>凉城邮政所</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16115</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16116</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>凉城邮政所</t>
+          <t>四川路桥邮政支局</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16116</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16117</t>
         </is>
       </c>
     </row>
@@ -9640,17 +9640,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>虹口区</t>
+          <t>奉贤区</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>虹口区</t>
+          <t>奉贤区</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>四川路桥邮政支局</t>
+          <t>南桥邮政支局</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16117</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16118</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>南桥邮政支局</t>
+          <t>育秀邮政所</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16118</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16119</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>育秀邮政所</t>
+          <t>贝港邮政所</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16119</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16120</t>
         </is>
       </c>
     </row>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>贝港邮政所</t>
+          <t>江海邮政所</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16120</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16121</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>江海邮政所</t>
+          <t>解放中路邮政所</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16121</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16122</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>解放中路邮政所</t>
+          <t>肖塘邮政支局</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16122</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16123</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>肖塘邮政支局</t>
+          <t>西渡邮政所</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16123</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16124</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>西渡邮政所</t>
+          <t>金汇邮政支局</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16124</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16125</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>金汇邮政支局</t>
+          <t>齐贤邮政支局</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16125</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16126</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>齐贤邮政支局</t>
+          <t>泰日邮政支局</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16126</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16127</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>泰日邮政支局</t>
+          <t>奉城邮政支局</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16127</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16128</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>奉城邮政支局</t>
+          <t>洪庙邮政所</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16128</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16129</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>洪庙邮政所</t>
+          <t>塘外邮政支局</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16129</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16130</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>塘外邮政支局</t>
+          <t>头桥邮政支局</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16130</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16131</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>头桥邮政支局</t>
+          <t>平安邮政支局</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16131</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16132</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>平安邮政支局</t>
+          <t>四团邮政支局</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16132</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16133</t>
         </is>
       </c>
     </row>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>四团邮政支局</t>
+          <t>邵厂邮政所</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16133</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16134</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>邵厂邮政所</t>
+          <t>五四邮政所</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16134</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16135</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>五四邮政所</t>
+          <t>青村邮政支局</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16135</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16136</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>青村邮政支局</t>
+          <t>光明邮政支局</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16136</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16137</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>光明邮政支局</t>
+          <t>钱桥邮政支局</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16137</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16138</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>钱桥邮政支局</t>
+          <t>庄行邮政支局</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16138</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16139</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>庄行邮政支局</t>
+          <t>邬桥邮政支局</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16139</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16140</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>邬桥邮政支局</t>
+          <t>海湾邮政支局</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16140</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16141</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>海湾邮政支局</t>
+          <t>新院邮政所</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16141</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16142</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>新院邮政所</t>
+          <t>柘林邮政支局</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16142</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16143</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>柘林邮政支局</t>
+          <t>新寺邮政支局</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16143</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16144</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>新寺邮政支局</t>
+          <t>胡桥邮政支局</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16144</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16145</t>
         </is>
       </c>
     </row>
@@ -10536,17 +10536,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>奉贤区</t>
+          <t>黄浦区</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>奉贤区</t>
+          <t>黄浦区</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>胡桥邮政支局</t>
+          <t>黄浦邮政支局</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16145</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16146</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>黄浦邮政支局</t>
+          <t>云南中路邮政所</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16146</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16147</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>云南中路邮政所</t>
+          <t>福州路邮政所</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16147</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16148</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>福州路邮政所</t>
+          <t>延安东路邮政所</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16148</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16149</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>延安东路邮政所</t>
+          <t>外滩邮政支局</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16149</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16150</t>
         </is>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>外滩邮政支局</t>
+          <t>金陵东路邮政所</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16150</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16151</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>金陵东路邮政所</t>
+          <t>人民公园邮政支局</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16151</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16152</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>人民公园邮政支局</t>
+          <t>黄河路邮政所</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16152</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16154</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>黄河路邮政所</t>
+          <t>南市邮政支局</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16154</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16155</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>南市邮政支局</t>
+          <t>老北门邮政所</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16155</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16156</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>老北门邮政所</t>
+          <t>方浜中路邮政所</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16156</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16157</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>方浜中路邮政所</t>
+          <t>新开河路邮政所</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16157</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16158</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>新开河路邮政所</t>
+          <t>南车站路邮政支局</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16158</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16159</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>南车站路邮政支局</t>
+          <t>老西门邮政所</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16159</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16160</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>老西门邮政所</t>
+          <t>斜桥邮政所</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16160</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16161</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>斜桥邮政所</t>
+          <t>高雄路邮政所</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16161</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16162</t>
         </is>
       </c>
     </row>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>高雄路邮政所</t>
+          <t>大南门邮政所</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16162</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16163</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>大南门邮政所</t>
+          <t>卢湾邮政支局</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16163</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16164</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>卢湾邮政支局</t>
+          <t>龙门路邮政支局</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16164</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16165</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>龙门路邮政支局</t>
+          <t>顺昌路邮政所</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16165</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16166</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>顺昌路邮政所</t>
+          <t>丽园路邮政支局</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16166</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16167</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>丽园路邮政支局</t>
+          <t>卢浦大桥邮政所</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16167</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16168</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>卢浦大桥邮政所</t>
+          <t>制造局路邮政所</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16168</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16169</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>制造局路邮政所</t>
+          <t>建国东路邮政支局</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16169</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16170</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>建国东路邮政支局</t>
+          <t>淡水路邮政所</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16170</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16172</t>
         </is>
       </c>
     </row>
@@ -11336,17 +11336,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>黄浦区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>黄浦区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>淡水路邮政所</t>
+          <t>陆家嘴邮政支局</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16172</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16173</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>陆家嘴邮政支局</t>
+          <t>乳山邮政所</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16173</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16174</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>乳山邮政所</t>
+          <t>浦东大道邮政所</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16174</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16175</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>浦东大道邮政所</t>
+          <t>浦电路邮政支局</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16175</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16176</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>浦电路邮政支局</t>
+          <t>潍坊邮政所</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16176</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16177</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>潍坊邮政所</t>
+          <t>竹园邮政所</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16177</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16178</t>
         </is>
       </c>
     </row>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>竹园邮政所</t>
+          <t>永泰路邮政支局</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16178</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16179</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>永泰路邮政支局</t>
+          <t>凌兆邮政支局</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16179</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16181</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>凌兆邮政支局</t>
+          <t>和炯路邮政所</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16181</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16182</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>和炯路邮政所</t>
+          <t>临沂路邮政支局</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16182</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16183</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>临沂路邮政支局</t>
+          <t>南码头邮政所</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16183</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16184</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>南码头邮政所</t>
+          <t>北艾路邮政支局</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16184</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16186</t>
         </is>
       </c>
     </row>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>北艾路邮政支局</t>
+          <t>世博邮政支局</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16186</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16187</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>世博邮政支局</t>
+          <t>杨思邮政所</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16187</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16188</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>杨思邮政所</t>
+          <t>云莲路邮政所</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16188</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16189</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>云莲路邮政所</t>
+          <t>上钢新村邮政所</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16189</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16190</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>上钢新村邮政所</t>
+          <t>蓝村路邮政支局</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16190</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16191</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>蓝村路邮政支局</t>
+          <t>塘桥邮政所</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16191</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16192</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>塘桥邮政所</t>
+          <t>东陆邮政支局</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16192</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16193</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>东陆邮政支局</t>
+          <t>沪东新村邮政所</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16193</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16194</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>沪东新村邮政所</t>
+          <t>博兴路邮政所</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16194</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16195</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>博兴路邮政所</t>
+          <t>莱阳路邮政所</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16195</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16196</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>莱阳路邮政所</t>
+          <t>张杨路邮政支局</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16196</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16197</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>张杨路邮政支局</t>
+          <t>联洋邮政所</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16197</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16198</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>联洋邮政所</t>
+          <t>泾东邮政所</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16198</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16199</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>泾东邮政所</t>
+          <t>浦东行政中心邮政所</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16199</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16200</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>浦东行政中心邮政所</t>
+          <t>洋泾邮政所</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16200</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16201</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>洋泾邮政所</t>
+          <t>金杨邮政支局</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16201</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16202</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>金杨邮政支局</t>
+          <t>金台路邮政所</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16202</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16203</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>金台路邮政所</t>
+          <t>云山路邮政所</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16203</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16204</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>云山路邮政所</t>
+          <t>庆宁寺邮政所</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16204</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16205</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>庆宁寺邮政所</t>
+          <t>金桥邮政支局</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16205</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16206</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>金桥邮政支局</t>
+          <t>张桥邮政所</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16206</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16207</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>张桥邮政所</t>
+          <t>碧云路邮政所</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16207</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16208</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>碧云路邮政所</t>
+          <t>自由贸易试验区邮政支局</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16208</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16209</t>
         </is>
       </c>
     </row>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>自由贸易试验区邮政支局</t>
+          <t>加枫路邮政所</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16209</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16210</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>加枫路邮政所</t>
+          <t>高桥邮政支局</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16210</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16211</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>高桥邮政支局</t>
+          <t>凌桥邮政所</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16211</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16212</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>凌桥邮政所</t>
+          <t>高东邮政所</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16212</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16213</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>高东邮政所</t>
+          <t>新川邮政支局</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16213</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16214</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>新川邮政支局</t>
+          <t>合庆邮政支局</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16214</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16215</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>合庆邮政支局</t>
+          <t>王港邮政所</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16215</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16216</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>王港邮政所</t>
+          <t>蔡路邮政所</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16216</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16217</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>蔡路邮政所</t>
+          <t>江镇邮政支局</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16217</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16218</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>江镇邮政支局</t>
+          <t>六团邮政所</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16218</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16219</t>
         </is>
       </c>
     </row>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>六团邮政所</t>
+          <t>春晓路邮政支局</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16219</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16220</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>春晓路邮政支局</t>
+          <t>北蔡邮政支局</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16220</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16221</t>
         </is>
       </c>
     </row>
@@ -12850,7 +12850,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>北蔡邮政支局</t>
+          <t>梅花路邮政所</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16221</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16222</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>梅花路邮政所</t>
+          <t>培花新村邮政所</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16222</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16223</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>培花新村邮政所</t>
+          <t>上海海关学院邮政所</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16223</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16224</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>上海海关学院邮政所</t>
+          <t>黄楼邮政支局</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16224</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16225</t>
         </is>
       </c>
     </row>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>黄楼邮政支局</t>
+          <t>浦东国际机场邮政支局</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16225</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16226</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>浦东国际机场邮政支局</t>
+          <t>施湾邮政所</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16226</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16227</t>
         </is>
       </c>
     </row>
@@ -13042,7 +13042,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>施湾邮政所</t>
+          <t>浦东国际机场候机楼邮政所</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -13052,7 +13052,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16227</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16228</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>浦东国际机场候机楼邮政所</t>
+          <t>浦东国际机场第二候机楼邮政所</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16228</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16229</t>
         </is>
       </c>
     </row>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>浦东国际机场第二候机楼邮政所</t>
+          <t>高行邮政支局</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16229</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16230</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>高行邮政支局</t>
+          <t>东沟邮政所</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16230</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16231</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>东沟邮政所</t>
+          <t>杨园邮政所</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16231</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16232</t>
         </is>
       </c>
     </row>
@@ -13202,7 +13202,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>杨园邮政所</t>
+          <t>园二路邮政所</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16232</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16233</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>园二路邮政所</t>
+          <t>华高邮政所</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16233</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16234</t>
         </is>
       </c>
     </row>
@@ -13266,7 +13266,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>华高邮政所</t>
+          <t>曹路邮政支局</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16234</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16235</t>
         </is>
       </c>
     </row>
@@ -13298,7 +13298,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>曹路邮政支局</t>
+          <t>龚路邮政所</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16235</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16236</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>龚路邮政所</t>
+          <t>民春路邮政所</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16236</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16237</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>民春路邮政所</t>
+          <t>张江邮政支局</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16237</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16238</t>
         </is>
       </c>
     </row>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>张江邮政支局</t>
+          <t>孙桥邮政所</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16238</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16239</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>孙桥邮政所</t>
+          <t>唐镇邮政所</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16239</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16240</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>唐镇邮政所</t>
+          <t>惠南邮政支局</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16240</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16241</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>惠南邮政支局</t>
+          <t>荡湾邮政所</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16241</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16242</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>荡湾邮政所</t>
+          <t>三灶邮政所</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16242</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16243</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>三灶邮政所</t>
+          <t>黄路邮政所</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16243</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16244</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13586,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>黄路邮政所</t>
+          <t>中港邮政支局</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16244</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16245</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>中港邮政支局</t>
+          <t>新港邮政所</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16245</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16246</t>
         </is>
       </c>
     </row>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>新港邮政所</t>
+          <t>泥城邮政支局</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16246</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16247</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>泥城邮政支局</t>
+          <t>海事大学邮政所</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16247</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16248</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>海事大学邮政所</t>
+          <t>海洋大学邮政所</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16248</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16249</t>
         </is>
       </c>
     </row>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>海洋大学邮政所</t>
+          <t>彭镇邮政所</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16249</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16250</t>
         </is>
       </c>
     </row>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>彭镇邮政所</t>
+          <t>港辉路邮政所</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16250</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16251</t>
         </is>
       </c>
     </row>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>港辉路邮政所</t>
+          <t>竹柏路邮政所</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16251</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16252</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>竹柏路邮政所</t>
+          <t>大团邮政支局</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16252</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16254</t>
         </is>
       </c>
     </row>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>大团邮政支局</t>
+          <t>三墩邮政所</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16254</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16255</t>
         </is>
       </c>
     </row>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>三墩邮政所</t>
+          <t>万祥邮政支局</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16255</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16256</t>
         </is>
       </c>
     </row>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>万祥邮政支局</t>
+          <t>东海农场邮政所</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16256</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16257</t>
         </is>
       </c>
     </row>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>东海农场邮政所</t>
+          <t>书院邮政所</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16257</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16258</t>
         </is>
       </c>
     </row>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>书院邮政所</t>
+          <t>新场邮政支局</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16258</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16259</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>新场邮政支局</t>
+          <t>坦直邮政所</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16259</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16260</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>坦直邮政所</t>
+          <t>康桥邮政支局</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16260</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16262</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>康桥邮政支局</t>
+          <t>横沔邮政所</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16262</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16264</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>横沔邮政所</t>
+          <t>下沙邮政支局</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16264</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16265</t>
         </is>
       </c>
     </row>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>下沙邮政支局</t>
+          <t>航头邮政所</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16265</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16266</t>
         </is>
       </c>
     </row>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>航头邮政所</t>
+          <t>鹤永路邮政所</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16266</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16267</t>
         </is>
       </c>
     </row>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>鹤永路邮政所</t>
+          <t>周浦邮政支局</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16267</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16268</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>周浦邮政支局</t>
+          <t>瓦屑邮政支局</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16268</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16269</t>
         </is>
       </c>
     </row>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>瓦屑邮政支局</t>
+          <t>祝桥邮政支局</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16269</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16270</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>祝桥邮政支局</t>
+          <t>六灶邮政所</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16270</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16271</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>六灶邮政所</t>
+          <t>盐仓邮政支局</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16271</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16272</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>盐仓邮政支局</t>
+          <t>东海邮政所</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16272</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16273</t>
         </is>
       </c>
     </row>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>东海邮政所</t>
+          <t>朝阳农场邮政所</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16273</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16274</t>
         </is>
       </c>
     </row>
@@ -14440,17 +14440,17 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>金山区</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>金山区</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>朝阳农场邮政所</t>
+          <t>漕泾邮政支局</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16274</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16275</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>漕泾邮政支局</t>
+          <t>东门邮政所</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16275</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16276</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>东门邮政所</t>
+          <t>枫泾邮政支局</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16276</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16277</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>枫泾邮政支局</t>
+          <t>干巷邮政支局</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16277</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16278</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>干巷邮政支局</t>
+          <t>金龙新街邮政所</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16278</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16280</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>金龙新街邮政所</t>
+          <t>金卫邮政支局</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16280</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16281</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>金卫邮政支局</t>
+          <t>廊下邮政支局</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16281</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16282</t>
         </is>
       </c>
     </row>
@@ -14674,7 +14674,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>廊下邮政支局</t>
+          <t>吕巷邮政支局</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16282</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16283</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>吕巷邮政支局</t>
+          <t>钱圩邮政支局</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16283</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16284</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>钱圩邮政支局</t>
+          <t>石化邮政支局</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16284</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16286</t>
         </is>
       </c>
     </row>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>石化邮政支局</t>
+          <t>松隐邮政支局</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -14780,7 +14780,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16286</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16287</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>松隐邮政支局</t>
+          <t>亭林邮政支局</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16287</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16288</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>亭林邮政支局</t>
+          <t>万安邮政所</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16288</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16289</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>万安邮政所</t>
+          <t>兴塔邮政支局</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16289</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16290</t>
         </is>
       </c>
     </row>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>兴塔邮政支局</t>
+          <t>张堰邮政支局</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16290</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16291</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>张堰邮政支局</t>
+          <t>朱行邮政支局</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16291</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16292</t>
         </is>
       </c>
     </row>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>朱行邮政支局</t>
+          <t>朱泾邮政支局</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16292</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16293</t>
         </is>
       </c>
     </row>
@@ -14984,17 +14984,17 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>金山区</t>
+          <t>普陀区</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>金山区</t>
+          <t>普陀区</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>朱泾邮政支局</t>
+          <t>普陀邮政支局</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16293</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16294</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>普陀邮政支局</t>
+          <t>叶家宅邮政所</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16294</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16295</t>
         </is>
       </c>
     </row>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>叶家宅邮政所</t>
+          <t>昌化路邮政所</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16295</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16296</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>昌化路邮政所</t>
+          <t>曹杨新村邮政支局</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16296</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16297</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>曹杨新村邮政支局</t>
+          <t>华东师大邮政所</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16297</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16298</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>华东师大邮政所</t>
+          <t>大渡河路邮政所</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16298</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16299</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>大渡河路邮政所</t>
+          <t>武宁路邮政支局</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16299</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16300</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>武宁路邮政支局</t>
+          <t>北石路邮政所</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16300</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16301</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>北石路邮政所</t>
+          <t>沪太邮政支局</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16301</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16302</t>
         </is>
       </c>
     </row>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>沪太邮政支局</t>
+          <t>石泉路邮政支局</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16302</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16303</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>石泉路邮政支局</t>
+          <t>宜川邮政所</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16303</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16304</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>宜川邮政所</t>
+          <t>桃浦邮政支局</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16304</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16306</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>桃浦邮政支局</t>
+          <t>红棉路邮政所</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16306</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16307</t>
         </is>
       </c>
     </row>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>红棉路邮政所</t>
+          <t>武威西路邮政所</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16307</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16308</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>武威西路邮政所</t>
+          <t>万泉路邮政所</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16308</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16309</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>万泉路邮政所</t>
+          <t>真如邮政支局</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16309</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16310</t>
         </is>
       </c>
     </row>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>真如邮政支局</t>
+          <t>万里邮政所</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16310</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16311</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>万里邮政所</t>
+          <t>真光邮政所</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16311</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16312</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>真光邮政所</t>
+          <t>火车西站邮政所</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -15580,7 +15580,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16312</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16313</t>
         </is>
       </c>
     </row>
@@ -15592,17 +15592,17 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>普陀区</t>
+          <t>青浦区</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>普陀区</t>
+          <t>青浦区</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>火车西站邮政所</t>
+          <t>青浦镇邮政支局</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16313</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16314</t>
         </is>
       </c>
     </row>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>青浦镇邮政支局</t>
+          <t>庆华邮政所</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16314</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16316</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>庆华邮政所</t>
+          <t>城中邮政所</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16316</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16317</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>城中邮政所</t>
+          <t>青东农场邮政所</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16317</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16318</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15730,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>青东农场邮政所</t>
+          <t>徐泾邮政支局</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16318</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16319</t>
         </is>
       </c>
     </row>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>徐泾邮政支局</t>
+          <t>赵巷邮政支局</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16319</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16320</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>赵巷邮政支局</t>
+          <t>重固邮政支局</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16320</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16322</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>重固邮政支局</t>
+          <t>香花邮政支局</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16322</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16323</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>香花邮政支局</t>
+          <t>白鹤邮政支局</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16323</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16324</t>
         </is>
       </c>
     </row>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>白鹤邮政支局</t>
+          <t>赵屯邮政支局</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16324</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16325</t>
         </is>
       </c>
     </row>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>赵屯邮政支局</t>
+          <t>大盈邮政支局</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16325</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16326</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>大盈邮政支局</t>
+          <t>华新邮政支局</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16326</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16327</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>华新邮政支局</t>
+          <t>凤溪邮政支局</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16327</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16328</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>凤溪邮政支局</t>
+          <t>朱家角邮政支局</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -16028,7 +16028,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16328</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16329</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>朱家角邮政支局</t>
+          <t>新风邮政所</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16329</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16330</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>新风邮政所</t>
+          <t>沈巷邮政支局</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16330</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16331</t>
         </is>
       </c>
     </row>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>沈巷邮政支局</t>
+          <t>练塘邮政支局</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16331</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16332</t>
         </is>
       </c>
     </row>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>练塘邮政支局</t>
+          <t>小蒸邮政支局</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16332</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16333</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16178,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>小蒸邮政支局</t>
+          <t>蒸淀邮政支局</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16333</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16334</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>蒸淀邮政支局</t>
+          <t>金泽邮政支局</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16334</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16335</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>金泽邮政支局</t>
+          <t>商榻邮政支局</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16335</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16336</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>商榻邮政支局</t>
+          <t>西岑邮政支局</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16336</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16337</t>
         </is>
       </c>
     </row>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>西岑邮政支局</t>
+          <t>莲盛邮政支局</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16337</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16338</t>
         </is>
       </c>
     </row>
@@ -16328,17 +16328,17 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>青浦区</t>
+          <t>杨浦区</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>青浦区</t>
+          <t>杨浦区</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>莲盛邮政支局</t>
+          <t>第二军医大学邮政所</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16338</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16923</t>
         </is>
       </c>
     </row>
@@ -16360,17 +16360,17 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>杨浦区</t>
+          <t>静安区</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>杨浦区</t>
+          <t>静安区</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>第二军医大学邮政所</t>
+          <t>常德路邮政所</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16923</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16924</t>
         </is>
       </c>
     </row>
@@ -16392,17 +16392,17 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>静安区</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>静安区</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>常德路邮政所</t>
+          <t>同济大学嘉定校区邮政所</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16924</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16930</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>同济大学嘉定校区邮政所</t>
+          <t>安礼路邮政所</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16930</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16931</t>
         </is>
       </c>
     </row>
@@ -16456,17 +16456,17 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>嘉定区</t>
+          <t>静安区</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>嘉定区</t>
+          <t>静安区</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>安礼路邮政所</t>
+          <t>静安邮政支局</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16931</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16932</t>
         </is>
       </c>
     </row>
@@ -16488,17 +16488,17 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>静安区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>静安区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>静安邮政支局</t>
+          <t>车墩邮政支局</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=16932</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=47732</t>
         </is>
       </c>
     </row>
@@ -16520,17 +16520,17 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>长宁区</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>长宁区</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>车墩邮政支局</t>
+          <t>延安西路邮政所</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=47732</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=51344</t>
         </is>
       </c>
     </row>
@@ -16552,17 +16552,17 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>长宁区</t>
+          <t>杨浦区</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>长宁区</t>
+          <t>杨浦区</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>延安西路邮政所</t>
+          <t>定海邮政所</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=51344</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=53995</t>
         </is>
       </c>
     </row>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>定海邮政所</t>
+          <t>杭州路邮政所</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=53995</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=53996</t>
         </is>
       </c>
     </row>
@@ -16616,17 +16616,17 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>杨浦区</t>
+          <t>闵行区</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>杨浦区</t>
+          <t>闵行区</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>杭州路邮政所</t>
+          <t>古龙路邮政所</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=53996</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54571</t>
         </is>
       </c>
     </row>
@@ -16648,17 +16648,17 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>闵行区</t>
+          <t>宝山区</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>闵行区</t>
+          <t>宝山区</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>古龙路邮政所</t>
+          <t>美平路邮政所</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54571</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54626</t>
         </is>
       </c>
     </row>
@@ -16680,17 +16680,17 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>宝山区</t>
+          <t>徐汇区</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>宝山区</t>
+          <t>徐汇区</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>美平路邮政所</t>
+          <t>中国邮政集团有限公司上海市徐汇区华滨家园邮政所</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54626</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54816</t>
         </is>
       </c>
     </row>
@@ -16712,17 +16712,17 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>徐汇区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>徐汇区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司上海市徐汇区华滨家园邮政所</t>
+          <t>周泰路邮政所</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54816</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54834</t>
         </is>
       </c>
     </row>
@@ -16744,17 +16744,17 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>周泰路邮政所</t>
+          <t>城鸿路邮政所</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54834</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54987</t>
         </is>
       </c>
     </row>
@@ -16776,17 +16776,17 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>崇明区</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>崇明区</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>城鸿路邮政所</t>
+          <t>仁建路邮政所</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=54987</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55018</t>
         </is>
       </c>
     </row>
@@ -16808,17 +16808,17 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>崇明区</t>
+          <t>长宁区</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>崇明区</t>
+          <t>长宁区</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>仁建路邮政所</t>
+          <t>虹桥临空邮政所</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55018</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55037</t>
         </is>
       </c>
     </row>
@@ -16840,17 +16840,17 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>长宁区</t>
+          <t>青浦区</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>长宁区</t>
+          <t>青浦区</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>虹桥临空邮政所</t>
+          <t>乐爱路邮政所</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55037</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55106</t>
         </is>
       </c>
     </row>
@@ -16872,17 +16872,17 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>青浦区</t>
+          <t>虹口区</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>青浦区</t>
+          <t>虹口区</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>乐爱路邮政所</t>
+          <t>虹湾路邮政所</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55106</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55275</t>
         </is>
       </c>
     </row>
@@ -16904,17 +16904,17 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>虹口区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>虹口区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>虹湾路邮政所</t>
+          <t>中国邮政集团有限公司上海市浦东新区东方路邮政所</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55275</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55478</t>
         </is>
       </c>
     </row>
@@ -16936,17 +16936,17 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>黄浦区</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>黄浦区</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司上海市浦东新区东方路邮政所</t>
+          <t>局门路邮政所</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55478</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55507</t>
         </is>
       </c>
     </row>
@@ -16968,17 +16968,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>黄浦区</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>黄浦区</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>局门路邮政所</t>
+          <t>芳林路邮政所</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55507</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55755</t>
         </is>
       </c>
     </row>
@@ -17000,17 +17000,17 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>嘉定区</t>
+          <t>青浦区</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>嘉定区</t>
+          <t>青浦区</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>芳林路邮政所</t>
+          <t>崧泉路邮政所</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55755</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55774</t>
         </is>
       </c>
     </row>
@@ -17032,17 +17032,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>青浦区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>青浦区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>崧泉路邮政所</t>
+          <t>听谐路邮政所</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55774</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55806</t>
         </is>
       </c>
     </row>
@@ -17064,17 +17064,17 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>听谐路邮政所</t>
+          <t>仓丰路邮政所</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55806</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55841</t>
         </is>
       </c>
     </row>
@@ -17096,17 +17096,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>金山区</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>金山区</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>仓丰路邮政所</t>
+          <t>中国邮政集团有限公司上海市金山区学府路邮政所</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=55841</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56083</t>
         </is>
       </c>
     </row>
@@ -17128,17 +17128,17 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>金山区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>金山区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司上海市金山区学府路邮政所</t>
+          <t>宣中路邮政所</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56083</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56107</t>
         </is>
       </c>
     </row>
@@ -17160,17 +17160,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>闵行区</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>闵行区</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>宣中路邮政所</t>
+          <t>立跃路邮政所</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56107</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56110</t>
         </is>
       </c>
     </row>
@@ -17192,17 +17192,17 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>闵行区</t>
+          <t>长宁区</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>闵行区</t>
+          <t>长宁区</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>立跃路邮政所</t>
+          <t>中国邮政集团有限公司上海市长宁区新泾三村邮政所</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56110</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56151</t>
         </is>
       </c>
     </row>
@@ -17224,17 +17224,17 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>长宁区</t>
+          <t>杨浦区</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>长宁区</t>
+          <t>杨浦区</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司上海市长宁区新泾三村邮政所</t>
+          <t>政和路邮政所</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56151</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56153</t>
         </is>
       </c>
     </row>
@@ -17256,17 +17256,17 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>杨浦区</t>
+          <t>普陀区</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>杨浦区</t>
+          <t>普陀区</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>政和路邮政所</t>
+          <t>祁连山南路邮政所</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
@@ -17276,7 +17276,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56153</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56260</t>
         </is>
       </c>
     </row>
@@ -17288,17 +17288,17 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>普陀区</t>
+          <t>金山区</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>普陀区</t>
+          <t>金山区</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>祁连山南路邮政所</t>
+          <t>中国邮政集团有限公司上海市金山区海丰路邮政支局</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56260</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56351</t>
         </is>
       </c>
     </row>
@@ -17320,17 +17320,17 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>金山区</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>金山区</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>中国邮政集团有限公司上海市金山区海丰路邮政支局</t>
+          <t>嘉好路邮政所</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56351</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56395</t>
         </is>
       </c>
     </row>
@@ -17352,17 +17352,17 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>嘉定区</t>
+          <t>虹口区</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>嘉定区</t>
+          <t>虹口区</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>嘉好路邮政所</t>
+          <t>同心路邮政所</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -17372,7 +17372,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56395</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56428</t>
         </is>
       </c>
     </row>
@@ -17384,17 +17384,17 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>虹口区</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>虹口区</t>
+          <t>嘉定区</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>同心路邮政所</t>
+          <t>民悦街邮政所</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56428</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56471</t>
         </is>
       </c>
     </row>
@@ -17416,17 +17416,17 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>嘉定区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>嘉定区</t>
+          <t>浦东新区</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>民悦街邮政所</t>
+          <t>鹤雷路邮政所</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56471</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56478</t>
         </is>
       </c>
     </row>
@@ -17448,17 +17448,17 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>浦东新区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>鹤雷路邮政所</t>
+          <t>香亭路邮政所</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56478</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56504</t>
         </is>
       </c>
     </row>
@@ -17480,17 +17480,17 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>徐汇区</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>徐汇区</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>香亭路邮政所</t>
+          <t>吴中路邮政所</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -17500,7 +17500,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56504</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56573</t>
         </is>
       </c>
     </row>
@@ -17512,27 +17512,27 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>徐汇区</t>
+          <t>崇明区</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>徐汇区</t>
+          <t>崇明区</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>吴中路邮政所</t>
+          <t>绿海路邮政所</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>信件、印刷品、包裹、邮政汇兑、国际业务、港澳台业务、报刊订阅</t>
+          <t>信件、印刷品、包裹、邮政汇兑、港澳台业务、报刊订阅</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56573</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56641</t>
         </is>
       </c>
     </row>
@@ -17544,27 +17544,27 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>崇明区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>崇明区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>绿海路邮政所</t>
+          <t>文浦路邮政支局</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>信件、印刷品、包裹、邮政汇兑、港澳台业务、报刊订阅</t>
+          <t>信件、印刷品、包裹、邮政汇兑、国际业务、港澳台业务、报刊订阅</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56641</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56686</t>
         </is>
       </c>
     </row>
@@ -17576,17 +17576,17 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>宝山区</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>松江区</t>
+          <t>宝山区</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>文浦路邮政支局</t>
+          <t>潘广路邮政所</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56686</t>
+          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56790</t>
         </is>
       </c>
     </row>
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>宝山区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>宝山区</t>
+          <t>松江区</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>潘广路邮政所</t>
+          <t>沪亭北路邮政所</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -17627,38 +17627,6 @@
         </is>
       </c>
       <c r="F538" t="inlineStr">
-        <is>
-          <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56790</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>松江区</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>松江区</t>
-        </is>
-      </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>沪亭北路邮政所</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>信件、印刷品、包裹、邮政汇兑、国际业务、港澳台业务、报刊订阅</t>
-        </is>
-      </c>
-      <c r="F539" t="inlineStr">
         <is>
           <t>https://zwfw.spb.gov.cn/sj/310000/pfyycsml/pfyycsmlDetail?uuid=56826</t>
         </is>
